--- a/output/archive/MerrivossData/Client_Work/TP04/MV-2024-358/MV-2024-358_AssayWorksheet_120524_R1.xlsx
+++ b/output/archive/MerrivossData/Client_Work/TP04/MV-2024-358/MV-2024-358_AssayWorksheet_120524_R1.xlsx
@@ -175,7 +175,7 @@
   <commentList>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Geometric mean of accepted cells; censored replicates excluded</t>
+        <t>Geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise &gt;30 µM (&gt;10 µM where precipitation limited the top concentration). n = accepted cells (finite).</t>
       </text>
     </comment>
   </commentList>
@@ -529,13 +529,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +552,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -591,12 +592,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Study Director</t>
+          <t>Study lead</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dr P. Nandekuri</t>
+          <t>Dr P. Nandekuri (DMPK Lead)</t>
         </is>
       </c>
     </row>
@@ -674,10 +675,11 @@
         <v>0.022</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Study summary (benchmark)</t>
+          <t>Study summary</t>
         </is>
       </c>
     </row>
@@ -899,6 +901,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -906,28 +909,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17.1" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18.8" customWidth="1" min="2" max="2"/>
+    <col width="18.8" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="4" max="4"/>
+    <col width="19.85" customWidth="1" min="5" max="5"/>
+    <col width="21.95" customWidth="1" min="6" max="6"/>
+    <col width="18.8" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>IKr inhibition: tail-current IC50, 6-point, top 30 µM</t>
-        </is>
-      </c>
-    </row>
+          <t>IKr inhibition: tail-current IC50 per cell, 6-point, top 30 µM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -936,22 +940,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 1 (µM)</t>
+          <t>IC50 cell 1 (µM)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 2 (µM)</t>
+          <t>IC50 cell 2 (µM)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 3 (µM)</t>
+          <t>IC50 cell 3 (µM)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>IC50 mean (µM)</t>
+          <t>IC50 geomean (µM)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -961,7 +965,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n cells (finite)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -989,8 +993,10 @@
       <c r="F4" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -1013,8 +1019,10 @@
       <c r="F5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
@@ -1037,8 +1045,10 @@
       <c r="F6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
@@ -1067,8 +1077,10 @@
       <c r="F7" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
@@ -1091,8 +1103,10 @@
       <c r="F8" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>2</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
@@ -1115,8 +1129,10 @@
       <c r="F9" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
@@ -1141,8 +1157,10 @@
       <c r="F10" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -1167,8 +1185,10 @@
       <c r="F11" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>3</v>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
@@ -1191,8 +1211,10 @@
       <c r="F12" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
@@ -1215,8 +1237,10 @@
       <c r="F13" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
@@ -1239,8 +1263,10 @@
       <c r="F14" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
@@ -1265,8 +1291,10 @@
       <c r="F15" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>3</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
@@ -1295,8 +1323,10 @@
       <c r="F16" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -1319,8 +1349,10 @@
       <c r="F17" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
@@ -1347,8 +1379,10 @@
       <c r="F18" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>3</v>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3 (2)</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
@@ -1375,8 +1409,10 @@
       <c r="F19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>2</v>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
@@ -1401,8 +1437,10 @@
       <c r="F20" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>3</v>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
@@ -1425,8 +1463,10 @@
       <c r="F21" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
@@ -1453,8 +1493,10 @@
       <c r="F22" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
@@ -1483,8 +1525,10 @@
       <c r="F23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>2</v>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -1507,8 +1551,10 @@
       <c r="F24" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>2</v>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
@@ -1531,8 +1577,10 @@
       <c r="F25" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>2</v>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
@@ -1555,8 +1603,10 @@
       <c r="F26" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>2</v>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
@@ -1579,8 +1629,10 @@
       <c r="F27" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>2</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1609,8 +1661,10 @@
       <c r="F28" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>2</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
@@ -1633,8 +1687,10 @@
       <c r="F29" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>2</v>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
@@ -1657,8 +1713,10 @@
       <c r="F30" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>2</v>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
@@ -1681,8 +1739,10 @@
       <c r="F31" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>2</v>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
@@ -1705,8 +1765,10 @@
       <c r="F32" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>2</v>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
@@ -1729,8 +1791,10 @@
       <c r="F33" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>2</v>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
     </row>
@@ -1753,8 +1817,10 @@
       <c r="F34" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>2</v>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
@@ -1777,8 +1843,10 @@
       <c r="F35" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>2</v>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
@@ -1801,8 +1869,10 @@
       <c r="F36" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
@@ -1833,8 +1903,10 @@
       <c r="F37" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>3</v>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3 (1)</t>
+        </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
@@ -1863,8 +1935,10 @@
       <c r="F38" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>2</v>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
@@ -1887,8 +1961,10 @@
       <c r="F39" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>2</v>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
@@ -1913,8 +1989,10 @@
       <c r="F40" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>3</v>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
@@ -1943,8 +2021,10 @@
       <c r="F41" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>2</v>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1973,8 +2053,10 @@
       <c r="F42" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>2</v>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
@@ -2001,11 +2083,14 @@
       <c r="F43" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>2</v>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -2013,8 +2098,16 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Compound IC50 = geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise reported as &gt;30 µM (or &gt;10 µM where solubility-limited)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2024,15 +2117,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.55" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2044,6 +2137,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2956,6 +3050,7 @@
         <v>11</v>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -2972,6 +3067,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2980,14 +3076,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="17.75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3052,7 +3148,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3159,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3174,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3116,7 +3212,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3246,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3257,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3176,7 +3272,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -3208,11 +3304,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3325,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3357,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3374,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3402,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -3361,7 +3457,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3372,11 +3468,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3489,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3506,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3517,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -3436,11 +3532,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3547,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -3489,7 +3585,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3630,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -3572,7 +3668,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>midazolam</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3696,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3655,19 +3751,21 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>testosterone</t>
-        </is>
-      </c>
-    </row>
+          <t>midazolam</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>7-point curve, top 50 µM; ketoconazole control</t>
+          <t>7-point curve, top 50 µM; ketoconazole control run alongside on every plate</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3675,15 +3773,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3704,10 +3805,20 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Historical mean</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3729,10 +3840,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>nM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>5-50 nM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3754,10 +3871,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3779,10 +3904,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3804,10 +3937,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3829,10 +3970,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3854,23 +4003,33 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>All runs met matrix acceptance criteria. Checked by Helen Marchwood.</t>
+          <t>All accepted runs met matrix acceptance criteria. Checked by Helen Marchwood.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>